--- a/110-creation-exemples/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:21:44+00:00</t>
+    <t>2024-07-01T16:22:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T16:22:22+00:00</t>
+    <t>2024-07-02T08:22:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -970,7 +970,7 @@
     <t>PractitionerRole.identifier:idSituationExercice.system</t>
   </si>
   <si>
-    <t>http://rpps.fr</t>
+    <t>https://rpps.esante.gouv.fr</t>
   </si>
   <si>
     <t>PractitionerRole.identifier:idSituationExercice.value</t>
@@ -1009,7 +1009,7 @@
     <t>PractitionerRole.identifier:numeroAm.system</t>
   </si>
   <si>
-    <t>http://ameli.fr</t>
+    <t>https://www.ameli.fr</t>
   </si>
   <si>
     <t>PractitionerRole.identifier:numeroAm.value</t>
@@ -1102,8 +1102,8 @@
     <t>Period.start</t>
   </si>
   <si>
-    <t xml:space="preserve">per-1
-</t>
+    <t>ele-1
+per-1</t>
   </si>
   <si>
     <t>dateDebutActivite</t>
@@ -8347,7 +8347,7 @@
         <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>78</v>
+        <v>208</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>119</v>
@@ -8359,7 +8359,7 @@
         <v>78</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>108</v>
+        <v>198</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>

--- a/110-creation-exemples/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T08:22:21+00:00</t>
+    <t>2024-07-02T09:45:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3295" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3295" uniqueCount="501">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T09:45:37+00:00</t>
+    <t>2024-07-02T11:34:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -991,7 +991,7 @@
     <t>[Donnée restreinte] : Identifiant d’activité propre à l’Assurance Maladie. format: 9 digits. synonyme: numeroAM</t>
   </si>
   <si>
-    <t>numeroAM</t>
+    <t>SituationExercice.numeroAM</t>
   </si>
   <si>
     <t>PractitionerRole.identifier:numeroAm.id</t>
@@ -1106,7 +1106,7 @@
 per-1</t>
   </si>
   <si>
-    <t>dateDebutActivite</t>
+    <t>SituationExercice.dateDebutActivite</t>
   </si>
   <si>
     <t>DR.1</t>
@@ -1133,7 +1133,7 @@
     <t>Period.end</t>
   </si>
   <si>
-    <t>dateFinActivite</t>
+    <t>SituationExercice.dateFinActivite</t>
   </si>
   <si>
     <t>DR.2</t>
@@ -1214,6 +1214,9 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J94-GenreActivite-RASS/FHIR/JDV-J94-GenreActivite-RASS</t>
   </si>
   <si>
+    <t>SituationExercice.genreActivite</t>
+  </si>
+  <si>
     <t>PractitionerRole.code:modeExercice</t>
   </si>
   <si>
@@ -1226,6 +1229,9 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J95-ModeExercice-RASS/FHIR/JDV-J95-ModeExercice-RASS</t>
   </si>
   <si>
+    <t>SituationExercice.modeExercice</t>
+  </si>
+  <si>
     <t>PractitionerRole.code:typeActiviteLiberale</t>
   </si>
   <si>
@@ -1238,6 +1244,9 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J96-TypeActiviteLiberale-RASS/FHIR/JDV-J96-TypeActiviteLiberale-RASS</t>
   </si>
   <si>
+    <t>SituationExercice.typeActiviteLiberale</t>
+  </si>
+  <si>
     <t>PractitionerRole.code:statutProfessionnelSSA</t>
   </si>
   <si>
@@ -1250,7 +1259,7 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J97-StatutProfessionnelSSA-RASS/FHIR/JDV-J97-StatutProfessionnelSSA-RASS</t>
   </si>
   <si>
-    <t>statutPS_SSA</t>
+    <t>SituationExercice.statutPS_SSA</t>
   </si>
   <si>
     <t>PractitionerRole.code:statutHospitalier</t>
@@ -1265,6 +1274,9 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J98-StatutHospitalier-RASS/FHIR/JDV-J98-StatutHospitalier-RASS</t>
   </si>
   <si>
+    <t>SituationExercice.statutHospitalier</t>
+  </si>
+  <si>
     <t>PractitionerRole.code:fonction</t>
   </si>
   <si>
@@ -1277,7 +1289,7 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J108-EnsembleFonction-RASS/FHIR/JDV-J108-EnsembleFonction-RASS</t>
   </si>
   <si>
-    <t>role</t>
+    <t>SituationExercice.role</t>
   </si>
   <si>
     <t>PractitionerRole.code:metierPharmacien</t>
@@ -1290,6 +1302,9 @@
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J73-MetierPharmacien-RASS/FHIR/JDV-J73-MetierPharmacien-RASS</t>
+  </si>
+  <si>
+    <t>SituationExercice.metierPharmacien</t>
   </si>
   <si>
     <t>PractitionerRole.specialty</t>
@@ -1378,7 +1393,7 @@
 ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
   </si>
   <si>
-    <t>telecommunication</t>
+    <t>SituationExercice.telecommunication</t>
   </si>
   <si>
     <t>XTN</t>
@@ -1403,7 +1418,7 @@
     <t>BALs MSS de type PER rattachés à l'identifiant du professionnel de santé  ainsi qu'au lieu de sa situation d'exercice (BoiteLettreMSS).</t>
   </si>
   <si>
-    <t>boiteLettresMSS</t>
+    <t>SituationExercice.boiteLettresMSS</t>
   </si>
   <si>
     <t>PractitionerRole.availableTime</t>
@@ -9053,7 +9068,7 @@
         <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>379</v>
@@ -9070,13 +9085,13 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>372</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>78</v>
@@ -9101,7 +9116,7 @@
         <v>253</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M62" t="s" s="2">
         <v>374</v>
@@ -9139,7 +9154,7 @@
       </c>
       <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>78</v>
@@ -9172,7 +9187,7 @@
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>379</v>
@@ -9189,13 +9204,13 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>372</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>78</v>
@@ -9220,7 +9235,7 @@
         <v>253</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M63" t="s" s="2">
         <v>374</v>
@@ -9258,7 +9273,7 @@
       </c>
       <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>78</v>
@@ -9291,7 +9306,7 @@
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>379</v>
@@ -9308,13 +9323,13 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>372</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>78</v>
@@ -9339,7 +9354,7 @@
         <v>253</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="M64" t="s" s="2">
         <v>374</v>
@@ -9377,7 +9392,7 @@
       </c>
       <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>78</v>
@@ -9410,7 +9425,7 @@
         <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>379</v>
@@ -9427,13 +9442,13 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>372</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>78</v>
@@ -9458,7 +9473,7 @@
         <v>253</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="M65" t="s" s="2">
         <v>374</v>
@@ -9496,7 +9511,7 @@
       </c>
       <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>78</v>
@@ -9529,7 +9544,7 @@
         <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>379</v>
@@ -9546,13 +9561,13 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>372</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>78</v>
@@ -9577,7 +9592,7 @@
         <v>253</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="M66" t="s" s="2">
         <v>374</v>
@@ -9615,7 +9630,7 @@
       </c>
       <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>78</v>
@@ -9648,7 +9663,7 @@
         <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>379</v>
@@ -9665,13 +9680,13 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>372</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="D67" t="s" s="2">
         <v>78</v>
@@ -9696,7 +9711,7 @@
         <v>253</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="M67" t="s" s="2">
         <v>374</v>
@@ -9734,7 +9749,7 @@
       </c>
       <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>78</v>
@@ -9767,7 +9782,7 @@
         <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>379</v>
@@ -9784,10 +9799,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9813,10 +9828,10 @@
         <v>253</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9847,7 +9862,7 @@
       </c>
       <c r="Y68" s="2"/>
       <c r="Z68" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>78</v>
@@ -9865,7 +9880,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9883,13 +9898,13 @@
         <v>78</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>78</v>
@@ -9897,10 +9912,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9923,13 +9938,13 @@
         <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9980,7 +9995,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10001,21 +10016,21 @@
         <v>78</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10038,13 +10053,13 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10095,7 +10110,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10113,10 +10128,10 @@
         <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>78</v>
@@ -10127,10 +10142,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10153,17 +10168,17 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -10200,7 +10215,7 @@
         <v>78</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="AC71" s="2"/>
       <c r="AD71" t="s" s="2">
@@ -10210,7 +10225,7 @@
         <v>117</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10222,19 +10237,19 @@
         <v>208</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>78</v>
@@ -10242,13 +10257,13 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="D72" t="s" s="2">
         <v>78</v>
@@ -10270,17 +10285,17 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>78</v>
@@ -10329,7 +10344,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10341,19 +10356,19 @@
         <v>208</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AN72" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>78</v>
@@ -10361,10 +10376,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10387,16 +10402,16 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10446,7 +10461,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10467,7 +10482,7 @@
         <v>78</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>78</v>
@@ -10478,10 +10493,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10593,10 +10608,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10710,14 +10725,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -10739,10 +10754,10 @@
         <v>111</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>114</v>
@@ -10797,7 +10812,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -10829,10 +10844,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10858,10 +10873,10 @@
         <v>175</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10891,10 +10906,10 @@
         <v>247</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>78</v>
@@ -10912,7 +10927,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -10933,7 +10948,7 @@
         <v>78</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>78</v>
@@ -10944,10 +10959,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10973,10 +10988,10 @@
         <v>324</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11027,7 +11042,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11048,7 +11063,7 @@
         <v>78</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>
@@ -11059,10 +11074,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11085,16 +11100,16 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11144,7 +11159,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11165,7 +11180,7 @@
         <v>78</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>78</v>
@@ -11176,10 +11191,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11202,16 +11217,16 @@
         <v>78</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11261,7 +11276,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11282,7 +11297,7 @@
         <v>78</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>78</v>
@@ -11293,10 +11308,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11319,13 +11334,13 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11376,7 +11391,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11397,7 +11412,7 @@
         <v>78</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>78</v>
@@ -11408,10 +11423,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11523,10 +11538,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11640,14 +11655,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -11669,10 +11684,10 @@
         <v>111</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>114</v>
@@ -11727,7 +11742,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -11759,10 +11774,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11788,10 +11803,10 @@
         <v>104</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11842,7 +11857,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>90</v>
@@ -11874,10 +11889,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11903,10 +11918,10 @@
         <v>282</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -11957,7 +11972,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -11978,7 +11993,7 @@
         <v>78</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>78</v>
@@ -11989,10 +12004,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12018,10 +12033,10 @@
         <v>104</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12072,7 +12087,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12093,7 +12108,7 @@
         <v>78</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>78</v>
@@ -12104,10 +12119,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12130,17 +12145,17 @@
         <v>78</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>78</v>
@@ -12189,7 +12204,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>

--- a/110-creation-exemples/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:34:04+00:00</t>
+    <t>2024-07-02T11:51:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1192,7 +1192,7 @@
     <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-role-exercice</t>
   </si>
   <si>
-    <t xml:space="preserve">value:coding.system}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>

--- a/110-creation-exemples/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:51:09+00:00</t>
+    <t>2024-07-02T12:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:01:26+00:00</t>
+    <t>2024-07-02T12:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:28:16+00:00</t>
+    <t>2024-07-02T14:06:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T14:06:23+00:00</t>
+    <t>2024-07-09T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T09:28:43+00:00</t>
+    <t>2024-07-09T09:35:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
